--- a/Seminar Rechnerarchitektur - WiSe2526/06_Auswertung Oszilloskop/Auswertung Oszilloskop.xlsx
+++ b/Seminar Rechnerarchitektur - WiSe2526/06_Auswertung Oszilloskop/Auswertung Oszilloskop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pfeff\Desktop\63778 Seminar Rechnerarchitektur\Forschungen\07_Auswertung Oszilloskop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pfeff\Desktop\63778 Seminar Rechnerarchitektur\Forschungen\06_Auswertung Oszilloskop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF1F7FA-E53A-47FB-AA64-017BE68A898A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559E1603-3214-4A9C-930C-53B3BD150B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3336" yWindow="1740" windowWidth="17280" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>emlearn</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>Inferenz</t>
+  </si>
+  <si>
+    <t>Flash Verbrauch [Byte]</t>
+  </si>
+  <si>
+    <t>SRAM Verbrauch [Byte]</t>
   </si>
 </sst>
 </file>
@@ -260,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -297,6 +303,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -420,7 +444,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$2</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>238.9725</c:v>
@@ -530,7 +554,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>59.383499999999998</c:v>
@@ -641,7 +665,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$4</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>54.311999999999998</c:v>
@@ -751,7 +775,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$5</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>5.7919999999999998</c:v>
@@ -763,7 +787,7 @@
             <c:numRef>
               <c:f>Sheet1!$F$5</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>96</c:v>
@@ -861,7 +885,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$6</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>2.8984999999999999</c:v>
@@ -971,7 +995,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$7</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>1.3140000000000001</c:v>
@@ -1085,7 +1109,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$8</c:f>
               <c:numCache>
-                <c:formatCode>#,#00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>1.17</c:v>
@@ -1201,7 +1225,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="#,#00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="out"/>
         <c:tickLblPos val="nextTo"/>
@@ -1387,12 +1411,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -2377,12 +2396,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -3558,13 +3572,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>518160</xdr:colOff>
+      <xdr:colOff>281940</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
@@ -3859,7 +3873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -3868,10 +3882,12 @@
     <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>13</v>
       </c>
@@ -3893,8 +3909,14 @@
       <c r="G1" s="13" t="s">
         <v>11</v>
       </c>
+      <c r="H1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3919,8 +3941,14 @@
         <f>B4/B2</f>
         <v>0.30180878552971574</v>
       </c>
+      <c r="H2" s="14">
+        <v>281944</v>
+      </c>
+      <c r="I2" s="15">
+        <v>25788</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3945,8 +3973,14 @@
         <f>B4/B3</f>
         <v>0.89984591679506931</v>
       </c>
+      <c r="H3" s="16">
+        <v>120800</v>
+      </c>
+      <c r="I3" s="17">
+        <v>25724</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3970,8 +4004,14 @@
       <c r="G4" s="6">
         <v>1</v>
       </c>
+      <c r="H4" s="16">
+        <v>147848</v>
+      </c>
+      <c r="I4" s="17">
+        <v>25724</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -3996,8 +4036,14 @@
         <f>B4/B5</f>
         <v>9.125</v>
       </c>
+      <c r="H5" s="16">
+        <v>384108</v>
+      </c>
+      <c r="I5" s="17">
+        <v>25740</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4022,8 +4068,14 @@
         <f>B4/B6</f>
         <v>18.838709677419356</v>
       </c>
+      <c r="H6" s="16">
+        <v>384188</v>
+      </c>
+      <c r="I6" s="17">
+        <v>25740</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4048,8 +4100,14 @@
         <f>B4/B7</f>
         <v>32.444444444444443</v>
       </c>
+      <c r="H7" s="16">
+        <v>385372</v>
+      </c>
+      <c r="I7" s="17">
+        <v>25740</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -4073,6 +4131,12 @@
       <c r="G8" s="9">
         <f>B4/B8</f>
         <v>38.93333333333333</v>
+      </c>
+      <c r="H8" s="18">
+        <v>374820</v>
+      </c>
+      <c r="I8" s="19">
+        <v>25740</v>
       </c>
     </row>
   </sheetData>
